--- a/R_analysis/output/tables/Tabela_Modelo_Interacao_Raca_IVS.xlsx
+++ b/R_analysis/output/tables/Tabela_Modelo_Interacao_Raca_IVS.xlsx
@@ -403,22 +403,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.002348439345800261</v>
+        <v>0.002348439345800257</v>
       </c>
       <c r="C2">
-        <v>0.03589825919469913</v>
+        <v>0.03589825919469902</v>
       </c>
       <c r="D2">
-        <v>-168.6433942876996</v>
+        <v>-168.6433942877002</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.002175891960780372</v>
+        <v>0.002175891960780363</v>
       </c>
       <c r="G2">
-        <v>0.002535319887916834</v>
+        <v>0.002535319887916838</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -429,26 +429,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>raca_corParda</t>
+          <t>raca_corBlack</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.9859779949123196</v>
+        <v>0.4606179428885316</v>
       </c>
       <c r="C3">
-        <v>0.05278671577079166</v>
+        <v>0.06429500792457991</v>
       </c>
       <c r="D3">
-        <v>-0.2675150737356443</v>
+        <v>-12.05671111815832</v>
       </c>
       <c r="E3">
-        <v>0.7890726097930387</v>
+        <v>1.787805680941707E-33</v>
       </c>
       <c r="F3">
-        <v>0.8818860241737952</v>
+        <v>0.4008821481919565</v>
       </c>
       <c r="G3">
-        <v>1.102467438423009</v>
+        <v>0.5292466781328762</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -459,26 +459,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>raca_corPreta</t>
+          <t>raca_corMixed-race</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.4606179428885317</v>
+        <v>0.9859779949123201</v>
       </c>
       <c r="C4">
-        <v>0.06429500792458023</v>
+        <v>0.0527867157707915</v>
       </c>
       <c r="D4">
-        <v>-12.05671111815826</v>
+        <v>-0.2675150737356373</v>
       </c>
       <c r="E4">
-        <v>1.787805680943056E-33</v>
+        <v>0.7890726097930441</v>
       </c>
       <c r="F4">
-        <v>0.4008821481919716</v>
+        <v>0.8818860241737666</v>
       </c>
       <c r="G4">
-        <v>0.5292466781329308</v>
+        <v>1.102467438423023</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.8846199949654849</v>
+        <v>0.8846199949654859</v>
       </c>
       <c r="C5">
-        <v>0.05462588048462767</v>
+        <v>0.05462588048462754</v>
       </c>
       <c r="D5">
-        <v>-2.24430451863014</v>
+        <v>-2.244304518630124</v>
       </c>
       <c r="E5">
-        <v>0.02481281502589549</v>
+        <v>0.02481281502589651</v>
       </c>
       <c r="F5">
-        <v>0.7846216552055337</v>
+        <v>0.7846216552055312</v>
       </c>
       <c r="G5">
-        <v>0.9972173746147226</v>
+        <v>0.9972173746147446</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -519,26 +519,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ivs_cat3Alta</t>
+          <t>ivs_cat3High</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.9850748343597927</v>
+        <v>0.9850748343597929</v>
       </c>
       <c r="C6">
-        <v>0.08699131954165203</v>
+        <v>0.08699131954165215</v>
       </c>
       <c r="D6">
-        <v>-0.1728639915548267</v>
+        <v>-0.1728639915548237</v>
       </c>
       <c r="E6">
-        <v>0.8627583360756775</v>
+        <v>0.8627583360756799</v>
       </c>
       <c r="F6">
-        <v>0.8224663179773716</v>
+        <v>0.8224663179773102</v>
       </c>
       <c r="G6">
-        <v>1.17882710302572</v>
+        <v>1.178827103025686</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -549,26 +549,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>raca_corParda:ivs_cat3Media</t>
+          <t>raca_corBlack:ivs_cat3Media</t>
         </is>
       </c>
       <c r="B7">
-        <v>2.066558830806431</v>
+        <v>1.443960834125487</v>
       </c>
       <c r="C7">
-        <v>0.07254246651129967</v>
+        <v>0.09177233723092017</v>
       </c>
       <c r="D7">
-        <v>10.0063432950197</v>
+        <v>4.003275148115296</v>
       </c>
       <c r="E7">
-        <v>1.429384676691496E-23</v>
+        <v>6.247157477200559E-05</v>
       </c>
       <c r="F7">
-        <v>1.767733943853971</v>
+        <v>1.179230782239131</v>
       </c>
       <c r="G7">
-        <v>2.415901118423943</v>
+        <v>1.768106005915846</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -579,26 +579,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>raca_corPreta:ivs_cat3Media</t>
+          <t>raca_corMixed-race:ivs_cat3Media</t>
         </is>
       </c>
       <c r="B8">
-        <v>1.44396083412549</v>
+        <v>2.066558830806434</v>
       </c>
       <c r="C8">
-        <v>0.09177233723092061</v>
+        <v>0.07254246651129964</v>
       </c>
       <c r="D8">
-        <v>4.003275148115296</v>
+        <v>10.00634329501971</v>
       </c>
       <c r="E8">
-        <v>6.247157477200581E-05</v>
+        <v>1.429384676691214E-23</v>
       </c>
       <c r="F8">
-        <v>1.179230782239153</v>
+        <v>1.767733943853628</v>
       </c>
       <c r="G8">
-        <v>1.768106005915753</v>
+        <v>2.415901118423752</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -609,26 +609,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>raca_corParda:ivs_cat3Alta</t>
+          <t>raca_corBlack:ivs_cat3High</t>
         </is>
       </c>
       <c r="B9">
-        <v>2.335107272735955</v>
+        <v>2.156498116846426</v>
       </c>
       <c r="C9">
-        <v>0.1028224113045967</v>
+        <v>0.1319154779614208</v>
       </c>
       <c r="D9">
-        <v>8.247791707275631</v>
+        <v>5.825591323595757</v>
       </c>
       <c r="E9">
-        <v>1.613482804500007E-16</v>
+        <v>5.691072784215873E-09</v>
       </c>
       <c r="F9">
-        <v>1.889049052295024</v>
+        <v>1.639486662850266</v>
       </c>
       <c r="G9">
-        <v>2.88822191586068</v>
+        <v>2.83609342322253</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -639,26 +639,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>raca_corPreta:ivs_cat3Alta</t>
+          <t>raca_corMixed-race:ivs_cat3High</t>
         </is>
       </c>
       <c r="B10">
-        <v>2.156498116846426</v>
+        <v>2.335107272735947</v>
       </c>
       <c r="C10">
-        <v>0.1319154779614207</v>
+        <v>0.1028224113045964</v>
       </c>
       <c r="D10">
-        <v>5.825591323595762</v>
+        <v>8.247791707275619</v>
       </c>
       <c r="E10">
-        <v>5.691072784215691E-09</v>
+        <v>1.613482804500175E-16</v>
       </c>
       <c r="F10">
-        <v>1.639486662850157</v>
+        <v>1.889049052295101</v>
       </c>
       <c r="G10">
-        <v>2.836093423222699</v>
+        <v>2.888221915860725</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
